--- a/data/trans_orig/P36BPD07_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD07_R-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>231829</t>
+          <t>231104</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>259504</t>
+          <t>257985</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>235813</t>
+          <t>236626</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>259965</t>
+          <t>259653</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>475937</t>
+          <t>477039</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>512807</t>
+          <t>512223</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,94%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34257</t>
+          <t>35776</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61932</t>
+          <t>62657</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28738</t>
+          <t>29050</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52890</t>
+          <t>52077</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69657</t>
+          <t>70241</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106527</t>
+          <t>105425</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>404362</t>
+          <t>402081</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>438015</t>
+          <t>436756</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>442088</t>
+          <t>444092</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>472341</t>
+          <t>473065</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>856586</t>
+          <t>855932</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>901812</t>
+          <t>901499</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,11%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64560</t>
+          <t>65819</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98213</t>
+          <t>100494</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48227</t>
+          <t>47503</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>78480</t>
+          <t>76476</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>121332</t>
+          <t>121645</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166558</t>
+          <t>167212</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>292468</t>
+          <t>293323</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>306412</t>
+          <t>306735</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>324363</t>
+          <t>324106</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>334088</t>
+          <t>333578</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>621208</t>
+          <t>621454</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>638195</t>
+          <t>637913</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21487</t>
+          <t>20632</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>12203</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12069</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29056</t>
+          <t>28810</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>274220</t>
+          <t>273269</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>306772</t>
+          <t>306440</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>307192</t>
+          <t>307977</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>335777</t>
+          <t>335878</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>591403</t>
+          <t>593152</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>635456</t>
+          <t>635624</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,31%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63192</t>
+          <t>63524</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95744</t>
+          <t>96695</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48164</t>
+          <t>48063</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76749</t>
+          <t>75964</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118449</t>
+          <t>118281</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>162502</t>
+          <t>160753</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>158896</t>
+          <t>160022</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>181722</t>
+          <t>182332</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>176152</t>
+          <t>178227</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>196794</t>
+          <t>197467</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>342861</t>
+          <t>342555</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>373862</t>
+          <t>373390</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,87%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29499</t>
+          <t>28889</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52325</t>
+          <t>51199</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21793</t>
+          <t>21120</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>40360</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55946</t>
+          <t>56418</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86947</t>
+          <t>87253</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>217217</t>
+          <t>215696</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>238850</t>
+          <t>238466</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>239823</t>
+          <t>238011</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>257289</t>
+          <t>256704</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>461282</t>
+          <t>461587</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>489759</t>
+          <t>491121</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,59%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24273</t>
+          <t>24657</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45906</t>
+          <t>47427</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15826</t>
+          <t>16411</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33292</t>
+          <t>35104</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46479</t>
+          <t>45117</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74956</t>
+          <t>74651</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>529340</t>
+          <t>528727</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>566969</t>
+          <t>566716</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>531823</t>
+          <t>533231</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>572304</t>
+          <t>572996</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1072380</t>
+          <t>1074303</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1127386</t>
+          <t>1129155</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,63%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>75866</t>
+          <t>76119</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>113495</t>
+          <t>114108</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>103549</t>
+          <t>102857</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>144030</t>
+          <t>142622</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>191302</t>
+          <t>189533</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>246308</t>
+          <t>244385</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>610441</t>
+          <t>611619</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>655579</t>
+          <t>655180</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>683311</t>
+          <t>679957</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>722736</t>
+          <t>720965</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1306510</t>
+          <t>1306780</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1366733</t>
+          <t>1368243</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,58%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>118092</t>
+          <t>118491</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>163230</t>
+          <t>162052</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>102455</t>
+          <t>104226</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>141880</t>
+          <t>145234</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>232129</t>
+          <t>230619</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>292352</t>
+          <t>292082</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2800989</t>
+          <t>2803345</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2889160</t>
+          <t>2886551</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3014471</t>
+          <t>3014342</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3093012</t>
+          <t>3093238</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5843895</t>
+          <t>5838447</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5960210</t>
+          <t>5961622</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,48%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>481946</t>
+          <t>484555</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>570117</t>
+          <t>567761</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>429255</t>
+          <t>429029</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>507796</t>
+          <t>507925</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>933163</t>
+          <t>931751</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1049478</t>
+          <t>1054926</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -4049,32 +4049,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>255748</t>
+          <t>264352</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>231302</t>
+          <t>248265</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>271786</t>
+          <t>278099</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4084,32 +4084,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>254405</t>
+          <t>271314</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>238480</t>
+          <t>256049</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>265183</t>
+          <t>281651</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4119,32 +4119,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>510152</t>
+          <t>535666</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>482097</t>
+          <t>513885</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>531068</t>
+          <t>553074</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>87,11%</t>
         </is>
       </c>
     </row>
@@ -4162,32 +4162,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55695</t>
+          <t>54493</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39657</t>
+          <t>40746</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80141</t>
+          <t>70580</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4197,32 +4197,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35230</t>
+          <t>44747</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24452</t>
+          <t>34410</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51155</t>
+          <t>60012</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4232,32 +4232,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>90925</t>
+          <t>99240</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70009</t>
+          <t>81832</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118980</t>
+          <t>121021</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -4275,17 +4275,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4345,17 +4345,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>412278</t>
+          <t>424194</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>387092</t>
+          <t>397483</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>435272</t>
+          <t>445686</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>417076</t>
+          <t>443265</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>398672</t>
+          <t>423725</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>432208</t>
+          <t>458378</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4462,32 +4462,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>829353</t>
+          <t>867459</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>798301</t>
+          <t>836879</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>857712</t>
+          <t>895731</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,28%</t>
         </is>
       </c>
     </row>
@@ -4505,32 +4505,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>106112</t>
+          <t>106453</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83118</t>
+          <t>84961</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>131298</t>
+          <t>133164</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>96301</t>
+          <t>101690</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81169</t>
+          <t>86577</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>114705</t>
+          <t>121230</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4575,32 +4575,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>202414</t>
+          <t>208143</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>174055</t>
+          <t>179871</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>233466</t>
+          <t>238723</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513377</t>
+          <t>544955</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513377</t>
+          <t>544955</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513377</t>
+          <t>544955</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4688,17 +4688,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031767</t>
+          <t>1075602</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031767</t>
+          <t>1075602</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031767</t>
+          <t>1075602</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>255921</t>
+          <t>253037</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>239802</t>
+          <t>237992</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>269840</t>
+          <t>266180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>307526</t>
+          <t>313927</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>295858</t>
+          <t>302014</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>317054</t>
+          <t>323150</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4805,32 +4805,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>563447</t>
+          <t>566962</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>545230</t>
+          <t>548030</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>579146</t>
+          <t>583111</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59292</t>
+          <t>62092</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45373</t>
+          <t>48949</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75411</t>
+          <t>77137</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4883,17 +4883,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40920</t>
+          <t>41772</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31392</t>
+          <t>32549</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52588</t>
+          <t>53685</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4918,32 +4918,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>100212</t>
+          <t>103865</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84513</t>
+          <t>87716</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>118429</t>
+          <t>122797</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -4961,17 +4961,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315213</t>
+          <t>315129</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315213</t>
+          <t>315129</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315213</t>
+          <t>315129</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4996,17 +4996,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>348446</t>
+          <t>355699</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>348446</t>
+          <t>355699</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>348446</t>
+          <t>355699</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5031,17 +5031,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>663659</t>
+          <t>670827</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>663659</t>
+          <t>670827</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>663659</t>
+          <t>670827</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>259999</t>
+          <t>309324</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>239119</t>
+          <t>285742</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>276386</t>
+          <t>325955</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>419891</t>
+          <t>356542</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>397593</t>
+          <t>339894</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>441785</t>
+          <t>372076</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5148,32 +5148,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>679890</t>
+          <t>665866</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>651006</t>
+          <t>637977</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>711326</t>
+          <t>690342</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>86,94%</t>
         </is>
       </c>
     </row>
@@ -5191,32 +5191,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>52558</t>
+          <t>63821</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36171</t>
+          <t>47190</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73438</t>
+          <t>87403</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>54788</t>
+          <t>64315</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32894</t>
+          <t>48781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77086</t>
+          <t>80963</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5261,32 +5261,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>107346</t>
+          <t>128136</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>75910</t>
+          <t>103660</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>136230</t>
+          <t>156025</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -5304,17 +5304,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5339,17 +5339,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>474679</t>
+          <t>420857</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>474679</t>
+          <t>420857</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>474679</t>
+          <t>420857</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5374,17 +5374,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787236</t>
+          <t>794002</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787236</t>
+          <t>794002</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787236</t>
+          <t>794002</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5421,32 +5421,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>137394</t>
+          <t>157058</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>126174</t>
+          <t>143493</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>147031</t>
+          <t>166508</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5456,32 +5456,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>183578</t>
+          <t>197740</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>175379</t>
+          <t>189108</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189768</t>
+          <t>205204</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5491,32 +5491,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>320972</t>
+          <t>354798</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>306944</t>
+          <t>341404</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>332793</t>
+          <t>368224</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,14%</t>
         </is>
       </c>
     </row>
@@ -5534,32 +5534,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>41348</t>
+          <t>48607</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31711</t>
+          <t>39157</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52568</t>
+          <t>62172</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>24696</t>
+          <t>29083</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18506</t>
+          <t>21619</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32895</t>
+          <t>37715</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5604,32 +5604,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>66044</t>
+          <t>77690</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54223</t>
+          <t>64264</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>80072</t>
+          <t>91084</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -5647,17 +5647,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5682,17 +5682,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5717,17 +5717,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5764,32 +5764,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>230913</t>
+          <t>232116</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>218017</t>
+          <t>220435</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>240564</t>
+          <t>241706</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5799,32 +5799,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>238647</t>
+          <t>244667</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>229918</t>
+          <t>236953</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>244381</t>
+          <t>250383</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5834,32 +5834,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>469560</t>
+          <t>476783</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>456154</t>
+          <t>462601</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>481926</t>
+          <t>488194</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -5877,32 +5877,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>38723</t>
+          <t>38591</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29072</t>
+          <t>29001</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51619</t>
+          <t>50272</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5912,32 +5912,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>18409</t>
+          <t>19083</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12675</t>
+          <t>13367</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27138</t>
+          <t>26797</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5947,32 +5947,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>57132</t>
+          <t>57674</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44766</t>
+          <t>46263</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>70538</t>
+          <t>71856</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -5990,17 +5990,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6025,17 +6025,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6060,17 +6060,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6107,32 +6107,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>492227</t>
+          <t>577405</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>462141</t>
+          <t>550530</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>518081</t>
+          <t>601477</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6142,32 +6142,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>731023</t>
+          <t>625411</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>684488</t>
+          <t>602609</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>794463</t>
+          <t>647457</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6177,32 +6177,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1223250</t>
+          <t>1202817</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1171536</t>
+          <t>1164729</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1321200</t>
+          <t>1235494</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>83,11%</t>
         </is>
       </c>
     </row>
@@ -6220,32 +6220,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>129144</t>
+          <t>139191</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>103290</t>
+          <t>115119</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>159230</t>
+          <t>166066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6255,32 +6255,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>117346</t>
+          <t>144488</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>53906</t>
+          <t>122442</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>163881</t>
+          <t>167290</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6290,32 +6290,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>246490</t>
+          <t>283678</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>148540</t>
+          <t>251001</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>298204</t>
+          <t>321766</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -6333,17 +6333,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>621371</t>
+          <t>716596</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>621371</t>
+          <t>716596</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>621371</t>
+          <t>716596</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6368,17 +6368,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848369</t>
+          <t>769899</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848369</t>
+          <t>769899</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848369</t>
+          <t>769899</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6403,17 +6403,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1469740</t>
+          <t>1486495</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1469740</t>
+          <t>1486495</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1469740</t>
+          <t>1486495</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6450,32 +6450,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>507698</t>
+          <t>303518</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>343204</t>
+          <t>276501</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>728959</t>
+          <t>335830</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6485,32 +6485,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>334155</t>
+          <t>391555</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>309573</t>
+          <t>367209</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>359462</t>
+          <t>421598</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6520,32 +6520,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>841853</t>
+          <t>695072</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>686210</t>
+          <t>658004</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1178763</t>
+          <t>733849</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>45,11%</t>
         </is>
       </c>
     </row>
@@ -6563,32 +6563,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>419926</t>
+          <t>493355</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>198665</t>
+          <t>461043</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>584420</t>
+          <t>520372</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6598,32 +6598,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>382304</t>
+          <t>438379</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>356997</t>
+          <t>408336</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>406886</t>
+          <t>462725</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6633,32 +6633,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>802231</t>
+          <t>931735</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>465321</t>
+          <t>892958</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>957874</t>
+          <t>968803</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>59,55%</t>
         </is>
       </c>
     </row>
@@ -6676,17 +6676,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>927624</t>
+          <t>796873</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>927624</t>
+          <t>796873</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>927624</t>
+          <t>796873</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6711,17 +6711,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>716459</t>
+          <t>829934</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>716459</t>
+          <t>829934</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>716459</t>
+          <t>829934</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6746,17 +6746,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644084</t>
+          <t>1626807</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644084</t>
+          <t>1626807</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644084</t>
+          <t>1626807</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6793,32 +6793,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2552177</t>
+          <t>2521004</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2462346</t>
+          <t>2460119</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2756369</t>
+          <t>2583832</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6828,32 +6828,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2886300</t>
+          <t>2844420</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2813060</t>
+          <t>2794219</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3020270</t>
+          <t>2894783</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6863,32 +6863,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>5438477</t>
+          <t>5365424</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5307759</t>
+          <t>5287905</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5654380</t>
+          <t>5446729</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -6906,32 +6906,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>902799</t>
+          <t>1006603</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>698607</t>
+          <t>943775</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>992630</t>
+          <t>1067488</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>769995</t>
+          <t>883558</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>636025</t>
+          <t>833195</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>843235</t>
+          <t>933759</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6976,32 +6976,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1672794</t>
+          <t>1890161</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1456891</t>
+          <t>1808856</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1803512</t>
+          <t>1967680</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -7019,17 +7019,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3454976</t>
+          <t>3527607</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3454976</t>
+          <t>3527607</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3454976</t>
+          <t>3527607</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7054,17 +7054,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3656295</t>
+          <t>3727978</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3656295</t>
+          <t>3727978</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3656295</t>
+          <t>3727978</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7089,17 +7089,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7111271</t>
+          <t>7255585</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7111271</t>
+          <t>7255585</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7111271</t>
+          <t>7255585</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
